--- a/results/greedy/UAVs4_GRID13/revenue/UAVs4_GRID13_Greedy.xlsx
+++ b/results/greedy/UAVs4_GRID13/revenue/UAVs4_GRID13_Greedy.xlsx
@@ -552,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03913091594586149</v>
+        <v>0.03913754201494157</v>
       </c>
       <c r="C2" t="n">
         <v>37.31237782338093</v>
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03899466700386256</v>
+        <v>0.03829970897641033</v>
       </c>
       <c r="C2" t="n">
         <v>19.81373768976229</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02821125002810732</v>
+        <v>0.02766366698779166</v>
       </c>
       <c r="C2" t="n">
         <v>24.30529652786182</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0213467080029659</v>
+        <v>0.02113270800327882</v>
       </c>
       <c r="C2" t="n">
         <v>30.68477696734892</v>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02681274997303262</v>
+        <v>0.02632962499046698</v>
       </c>
       <c r="C2" t="n">
         <v>34.10583439082212</v>
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03795083297882229</v>
+        <v>0.03757683298317716</v>
       </c>
       <c r="C2" t="n">
         <v>19.93701596211644</v>
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03959875000873581</v>
+        <v>0.03963137499522418</v>
       </c>
       <c r="C2" t="n">
         <v>26.05189388260496</v>
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03092770802322775</v>
+        <v>0.03092979197390378</v>
       </c>
       <c r="C2" t="n">
         <v>25.96263197031789</v>
@@ -1080,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0319684169953689</v>
+        <v>0.03190325002651662</v>
       </c>
       <c r="C2" t="n">
         <v>26.18653902232788</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03115537500707433</v>
+        <v>0.03106274997116998</v>
       </c>
       <c r="C2" t="n">
         <v>22.04617800543048</v>
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03644604195142165</v>
+        <v>0.03668324998579919</v>
       </c>
       <c r="C2" t="n">
         <v>24.17249248002733</v>
@@ -1278,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02597237500594929</v>
+        <v>0.02609354199375957</v>
       </c>
       <c r="C2" t="n">
         <v>25.21522015592096</v>
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03836870798841119</v>
+        <v>0.03776712500257418</v>
       </c>
       <c r="C2" t="n">
         <v>27.75384601430106</v>
@@ -1410,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04556349996710196</v>
+        <v>0.04531754099298269</v>
       </c>
       <c r="C2" t="n">
         <v>34.74629941427805</v>
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03189283300889656</v>
+        <v>0.03125366702442989</v>
       </c>
       <c r="C2" t="n">
         <v>28.01665260795502</v>
@@ -1542,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.039902041957248</v>
+        <v>0.04052233404945582</v>
       </c>
       <c r="C2" t="n">
         <v>26.77130811102322</v>
@@ -1608,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03432783298194408</v>
+        <v>0.03423904103692621</v>
       </c>
       <c r="C2" t="n">
         <v>20.17567730866047</v>
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03183341596741229</v>
+        <v>0.03219883400015533</v>
       </c>
       <c r="C2" t="n">
         <v>23.36945794243448</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03008612501434982</v>
+        <v>0.02989920799154788</v>
       </c>
       <c r="C2" t="n">
         <v>24.13177016018296</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03466154198395088</v>
+        <v>0.03382954199332744</v>
       </c>
       <c r="C2" t="n">
         <v>31.31237025496629</v>
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02763845899607986</v>
+        <v>0.02672562503721565</v>
       </c>
       <c r="C2" t="n">
         <v>31.9859528628226</v>
@@ -1938,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02385933400364593</v>
+        <v>0.02287854201858863</v>
       </c>
       <c r="C2" t="n">
         <v>20.31418347617561</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03474370797630399</v>
+        <v>0.03430083399871364</v>
       </c>
       <c r="C2" t="n">
         <v>29.71629119912782</v>
@@ -2070,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02430537500185892</v>
+        <v>0.02450083399889991</v>
       </c>
       <c r="C2" t="n">
         <v>20.72540135154347</v>
@@ -2136,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03470479202223942</v>
+        <v>0.03403312497539446</v>
       </c>
       <c r="C2" t="n">
         <v>24.76065923426388</v>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03931699995882809</v>
+        <v>0.03804429102456197</v>
       </c>
       <c r="C2" t="n">
         <v>33.30713037440233</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03601762495236471</v>
+        <v>0.03535862499848008</v>
       </c>
       <c r="C2" t="n">
         <v>26.25134648164266</v>
@@ -2334,7 +2334,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04154645896051079</v>
+        <v>0.04020341602154076</v>
       </c>
       <c r="C2" t="n">
         <v>23.02695318961876</v>
@@ -2400,7 +2400,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03457974997581914</v>
+        <v>0.03380329202627763</v>
       </c>
       <c r="C2" t="n">
         <v>22.51649469343995</v>
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02618954103672877</v>
+        <v>0.02573491696966812</v>
       </c>
       <c r="C2" t="n">
         <v>28.70192658506124</v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03964770800666884</v>
+        <v>0.03953270800411701</v>
       </c>
       <c r="C2" t="n">
         <v>24.6608715473189</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04403962503420189</v>
+        <v>0.04324616701342165</v>
       </c>
       <c r="C2" t="n">
         <v>24.51137582550633</v>
@@ -2664,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03862270800163969</v>
+        <v>0.03754516702610999</v>
       </c>
       <c r="C2" t="n">
         <v>29.74375299702789</v>
@@ -2730,7 +2730,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03312666597776115</v>
+        <v>0.03204649995313957</v>
       </c>
       <c r="C2" t="n">
         <v>24.91154322693891</v>
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03304666699841619</v>
+        <v>0.03308841702528298</v>
       </c>
       <c r="C2" t="n">
         <v>27.48236608914779</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04322712501743808</v>
+        <v>0.04262779100099578</v>
       </c>
       <c r="C2" t="n">
         <v>33.08915691384912</v>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02817729098023847</v>
+        <v>0.02742812497308478</v>
       </c>
       <c r="C2" t="n">
         <v>18.05881459920804</v>
@@ -2994,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02998891699826345</v>
+        <v>0.02932620898354799</v>
       </c>
       <c r="C2" t="n">
         <v>25.7887567622325</v>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03225808398565277</v>
+        <v>0.03101245901780203</v>
       </c>
       <c r="C2" t="n">
         <v>30.68494652831196</v>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0294477500137873</v>
+        <v>0.02908012497937307</v>
       </c>
       <c r="C2" t="n">
         <v>28.15303935249008</v>
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03786233300343156</v>
+        <v>0.03739854198647663</v>
       </c>
       <c r="C2" t="n">
         <v>24.13078238771159</v>
@@ -3258,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03480466594919562</v>
+        <v>0.0341021660133265</v>
       </c>
       <c r="C2" t="n">
         <v>23.10637677915529</v>
@@ -3324,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04305116599425673</v>
+        <v>0.04193341598147526</v>
       </c>
       <c r="C2" t="n">
         <v>32.13854482346693</v>
@@ -3390,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03033445798791945</v>
+        <v>0.0298945420072414</v>
       </c>
       <c r="C2" t="n">
         <v>27.1688126855761</v>
@@ -3456,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02523604099405929</v>
+        <v>0.02481929102214053</v>
       </c>
       <c r="C2" t="n">
         <v>27.79007522835755</v>
@@ -3522,7 +3522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02612466597929597</v>
+        <v>0.02532275003613904</v>
       </c>
       <c r="C2" t="n">
         <v>24.58158924675276</v>
@@ -3588,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03247770899906754</v>
+        <v>0.03222229098901153</v>
       </c>
       <c r="C2" t="n">
         <v>28.07335806613609</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0325719999964349</v>
+        <v>0.03162679204251617</v>
       </c>
       <c r="C2" t="n">
         <v>28.29560009078929</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02951799996662885</v>
+        <v>0.02896945900283754</v>
       </c>
       <c r="C2" t="n">
         <v>26.16044320383183</v>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0368862499599345</v>
+        <v>0.03610800002934411</v>
       </c>
       <c r="C2" t="n">
         <v>30.67072474801884</v>
@@ -3852,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03104641597019508</v>
+        <v>0.03068650001659989</v>
       </c>
       <c r="C2" t="n">
         <v>22.24620403017808</v>
@@ -3918,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04166137502761558</v>
+        <v>0.04071804200066254</v>
       </c>
       <c r="C2" t="n">
         <v>23.44320602715669</v>
@@ -3984,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0382187920040451</v>
+        <v>0.03750550001859665</v>
       </c>
       <c r="C2" t="n">
         <v>26.41894103186296</v>
@@ -4050,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03346612502355129</v>
+        <v>0.03292470797896385</v>
       </c>
       <c r="C2" t="n">
         <v>31.69069203021384</v>
@@ -4116,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02743654197547585</v>
+        <v>0.02704187500057742</v>
       </c>
       <c r="C2" t="n">
         <v>26.59622656827356</v>
@@ -4182,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03163108299486339</v>
+        <v>0.03104587498819456</v>
       </c>
       <c r="C2" t="n">
         <v>25.84431517983234</v>
@@ -4248,7 +4248,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0339713339926675</v>
+        <v>0.03441024996573105</v>
       </c>
       <c r="C2" t="n">
         <v>23.066359406831</v>
@@ -4314,7 +4314,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03082883398747072</v>
+        <v>0.03069437498925254</v>
       </c>
       <c r="C2" t="n">
         <v>26.383680238381</v>
@@ -4380,7 +4380,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03896825003903359</v>
+        <v>0.0382320000207983</v>
       </c>
       <c r="C2" t="n">
         <v>24.11510503866736</v>
@@ -4446,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03718679200392216</v>
+        <v>0.03653316700365394</v>
       </c>
       <c r="C2" t="n">
         <v>31.15274486568289</v>
@@ -4512,7 +4512,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02627641602884978</v>
+        <v>0.02548075001686811</v>
       </c>
       <c r="C2" t="n">
         <v>25.10515123146655</v>
@@ -4578,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02378308394690976</v>
+        <v>0.02337462495779619</v>
       </c>
       <c r="C2" t="n">
         <v>21.40247859344191</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03579591697780415</v>
+        <v>0.03453416598495096</v>
       </c>
       <c r="C2" t="n">
         <v>28.84499232601139</v>
@@ -4710,7 +4710,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03536837501451373</v>
+        <v>0.0349068749928847</v>
       </c>
       <c r="C2" t="n">
         <v>31.96300888133719</v>
@@ -4776,7 +4776,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03780479199485853</v>
+        <v>0.03741333301877603</v>
       </c>
       <c r="C2" t="n">
         <v>19.1874685605234</v>
@@ -4842,7 +4842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03545920795295388</v>
+        <v>0.03500145900761709</v>
       </c>
       <c r="C2" t="n">
         <v>22.97599057801336</v>
@@ -4908,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03483849996700883</v>
+        <v>0.03431216697208583</v>
       </c>
       <c r="C2" t="n">
         <v>29.8014388645108</v>
@@ -4974,7 +4974,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03493470803368837</v>
+        <v>0.03529895801329985</v>
       </c>
       <c r="C2" t="n">
         <v>24.58878539776038</v>
@@ -5040,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02853441599290818</v>
+        <v>0.02848445903509855</v>
       </c>
       <c r="C2" t="n">
         <v>26.48750095162407</v>
@@ -5106,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02943758299807087</v>
+        <v>0.0289857080206275</v>
       </c>
       <c r="C2" t="n">
         <v>20.87484769185441</v>
@@ -5172,7 +5172,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02924029104178771</v>
+        <v>0.02876058302354068</v>
       </c>
       <c r="C2" t="n">
         <v>30.3521143176178</v>
@@ -5238,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0298404159839265</v>
+        <v>0.02944966702489182</v>
       </c>
       <c r="C2" t="n">
         <v>19.03386101859335</v>
@@ -5304,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0363353340071626</v>
+        <v>0.03524141601519659</v>
       </c>
       <c r="C2" t="n">
         <v>23.19640566381431</v>
@@ -5370,7 +5370,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03092937497422099</v>
+        <v>0.03059320797910914</v>
       </c>
       <c r="C2" t="n">
         <v>20.16017652381561</v>
@@ -5436,7 +5436,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04035141703207046</v>
+        <v>0.04003083298448473</v>
       </c>
       <c r="C2" t="n">
         <v>22.13780947150403</v>
@@ -5502,7 +5502,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03217954200226814</v>
+        <v>0.03131674998439848</v>
       </c>
       <c r="C2" t="n">
         <v>29.29725439327199</v>
@@ -5568,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03632420900976285</v>
+        <v>0.03511408303165808</v>
       </c>
       <c r="C2" t="n">
         <v>24.01116811918489</v>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03678075002972037</v>
+        <v>0.03627791604958475</v>
       </c>
       <c r="C2" t="n">
         <v>25.0046187156633</v>
@@ -5700,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02912274998379871</v>
+        <v>0.02909954101778567</v>
       </c>
       <c r="C2" t="n">
         <v>32.93361061351427</v>
@@ -5766,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03098737500840798</v>
+        <v>0.03028829203685746</v>
       </c>
       <c r="C2" t="n">
         <v>26.95558676956336</v>
@@ -5832,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03076279204105958</v>
+        <v>0.03057033300865442</v>
       </c>
       <c r="C2" t="n">
         <v>29.22535108295815</v>
@@ -5898,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02617287501925603</v>
+        <v>0.02522525005042553</v>
       </c>
       <c r="C2" t="n">
         <v>22.95345139908935</v>
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03754895797464997</v>
+        <v>0.036670041969046</v>
       </c>
       <c r="C2" t="n">
         <v>28.28166847430387</v>
@@ -6030,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03094408300239593</v>
+        <v>0.03048162499908358</v>
       </c>
       <c r="C2" t="n">
         <v>25.74364289621601</v>
@@ -6096,7 +6096,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03004154103109613</v>
+        <v>0.0293622090248391</v>
       </c>
       <c r="C2" t="n">
         <v>27.36872350918075</v>
@@ -6162,7 +6162,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02967383299255744</v>
+        <v>0.02920016698772088</v>
       </c>
       <c r="C2" t="n">
         <v>27.39725373853555</v>
@@ -6228,7 +6228,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03070462500909343</v>
+        <v>0.03027116699377075</v>
       </c>
       <c r="C2" t="n">
         <v>22.09668709982884</v>
@@ -6294,7 +6294,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02962429204490036</v>
+        <v>0.02976420801132917</v>
       </c>
       <c r="C2" t="n">
         <v>23.74450288537857</v>
@@ -6360,7 +6360,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03015691699692979</v>
+        <v>0.02971791697200388</v>
       </c>
       <c r="C2" t="n">
         <v>24.5022837145464</v>
@@ -6426,7 +6426,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03404800000134856</v>
+        <v>0.03522291599074379</v>
       </c>
       <c r="C2" t="n">
         <v>25.76556072725754</v>
@@ -6492,7 +6492,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0325430830125697</v>
+        <v>0.03172937501221895</v>
       </c>
       <c r="C2" t="n">
         <v>27.65887615876256</v>
@@ -6558,7 +6558,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0347346659982577</v>
+        <v>0.03434216597815976</v>
       </c>
       <c r="C2" t="n">
         <v>21.94297867107104</v>
@@ -6624,7 +6624,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03153841703897342</v>
+        <v>0.03092774999095127</v>
       </c>
       <c r="C2" t="n">
         <v>29.64842419577577</v>
@@ -6690,7 +6690,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02870979096041992</v>
+        <v>0.02852487500058487</v>
       </c>
       <c r="C2" t="n">
         <v>24.25086141006013</v>
@@ -6756,7 +6756,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03082041599554941</v>
+        <v>0.03072254196740687</v>
       </c>
       <c r="C2" t="n">
         <v>21.34958531531084</v>
@@ -6822,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0293903750134632</v>
+        <v>0.02890720800496638</v>
       </c>
       <c r="C2" t="n">
         <v>23.4016800916731</v>
@@ -6888,7 +6888,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04523616703227162</v>
+        <v>0.04456420801579952</v>
       </c>
       <c r="C2" t="n">
         <v>28.08427886819091</v>
@@ -6954,7 +6954,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03802112501580268</v>
+        <v>0.03679566696519032</v>
       </c>
       <c r="C2" t="n">
         <v>24.01826489266311</v>
@@ -7020,7 +7020,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0442187919979915</v>
+        <v>0.04320487502263859</v>
       </c>
       <c r="C2" t="n">
         <v>30.51309485044004</v>
@@ -7086,7 +7086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03702925000106916</v>
+        <v>0.0365390419610776</v>
       </c>
       <c r="C2" t="n">
         <v>30.63311186116157</v>

--- a/results/greedy/UAVs4_GRID13/revenue/UAVs4_GRID13_Greedy.xlsx
+++ b/results/greedy/UAVs4_GRID13/revenue/UAVs4_GRID13_Greedy.xlsx
@@ -552,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03913754201494157</v>
+        <v>0.03884370904415846</v>
       </c>
       <c r="C2" t="n">
         <v>37.31237782338093</v>
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03829970897641033</v>
+        <v>0.05805758299538866</v>
       </c>
       <c r="C2" t="n">
         <v>19.81373768976229</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02766366698779166</v>
+        <v>0.02765616704709828</v>
       </c>
       <c r="C2" t="n">
         <v>24.30529652786182</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02113270800327882</v>
+        <v>0.02084354200633243</v>
       </c>
       <c r="C2" t="n">
         <v>30.68477696734892</v>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02632962499046698</v>
+        <v>0.02561233297456056</v>
       </c>
       <c r="C2" t="n">
         <v>34.10583439082212</v>
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03757683298317716</v>
+        <v>0.03604766697390005</v>
       </c>
       <c r="C2" t="n">
         <v>19.93701596211644</v>
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03963137499522418</v>
+        <v>0.03841400000965223</v>
       </c>
       <c r="C2" t="n">
         <v>26.05189388260496</v>
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03092979197390378</v>
+        <v>0.03011587500805035</v>
       </c>
       <c r="C2" t="n">
         <v>25.96263197031789</v>
@@ -1080,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03190325002651662</v>
+        <v>0.03090224997140467</v>
       </c>
       <c r="C2" t="n">
         <v>26.18653902232788</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03106274997116998</v>
+        <v>0.02998366701649502</v>
       </c>
       <c r="C2" t="n">
         <v>22.04617800543048</v>
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03668324998579919</v>
+        <v>0.03535312501480803</v>
       </c>
       <c r="C2" t="n">
         <v>24.17249248002733</v>
@@ -1278,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02609354199375957</v>
+        <v>0.02565775002585724</v>
       </c>
       <c r="C2" t="n">
         <v>25.21522015592096</v>
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03776712500257418</v>
+        <v>0.03783916594693437</v>
       </c>
       <c r="C2" t="n">
         <v>27.75384601430106</v>
@@ -1410,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04531754099298269</v>
+        <v>0.04466429201420397</v>
       </c>
       <c r="C2" t="n">
         <v>34.74629941427805</v>
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03125366702442989</v>
+        <v>0.03084929101169109</v>
       </c>
       <c r="C2" t="n">
         <v>28.01665260795502</v>
@@ -1542,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04052233404945582</v>
+        <v>0.03898445796221495</v>
       </c>
       <c r="C2" t="n">
         <v>26.77130811102322</v>
@@ -1608,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03423904103692621</v>
+        <v>0.03320599999278784</v>
       </c>
       <c r="C2" t="n">
         <v>20.17567730866047</v>
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03219883400015533</v>
+        <v>0.03109845798462629</v>
       </c>
       <c r="C2" t="n">
         <v>23.36945794243448</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02989920799154788</v>
+        <v>0.02950708399293944</v>
       </c>
       <c r="C2" t="n">
         <v>24.13177016018296</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03382954199332744</v>
+        <v>0.03370545897632837</v>
       </c>
       <c r="C2" t="n">
         <v>31.31237025496629</v>
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02672562503721565</v>
+        <v>0.02708408399485052</v>
       </c>
       <c r="C2" t="n">
         <v>31.9859528628226</v>
@@ -1938,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02287854201858863</v>
+        <v>0.02309983398299664</v>
       </c>
       <c r="C2" t="n">
         <v>20.31418347617561</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03430083399871364</v>
+        <v>0.03396824997616932</v>
       </c>
       <c r="C2" t="n">
         <v>29.71629119912782</v>
@@ -2070,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02450083399889991</v>
+        <v>0.02371679100906476</v>
       </c>
       <c r="C2" t="n">
         <v>20.72540135154347</v>
@@ -2136,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03403312497539446</v>
+        <v>0.03381716698640957</v>
       </c>
       <c r="C2" t="n">
         <v>24.76065923426388</v>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03804429102456197</v>
+        <v>0.03810187504859641</v>
       </c>
       <c r="C2" t="n">
         <v>33.30713037440233</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03535862499848008</v>
+        <v>0.03521100000943989</v>
       </c>
       <c r="C2" t="n">
         <v>26.25134648164266</v>
@@ -2334,7 +2334,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04020341602154076</v>
+        <v>0.04016199999023229</v>
       </c>
       <c r="C2" t="n">
         <v>23.02695318961876</v>
@@ -2400,7 +2400,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03380329202627763</v>
+        <v>0.03387245797784999</v>
       </c>
       <c r="C2" t="n">
         <v>22.51649469343995</v>
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02573491696966812</v>
+        <v>0.0251637080218643</v>
       </c>
       <c r="C2" t="n">
         <v>28.70192658506124</v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03953270800411701</v>
+        <v>0.03884587500942871</v>
       </c>
       <c r="C2" t="n">
         <v>24.6608715473189</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04324616701342165</v>
+        <v>0.04293183301342651</v>
       </c>
       <c r="C2" t="n">
         <v>24.51137582550633</v>
@@ -2664,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03754516702610999</v>
+        <v>0.03778499999316409</v>
       </c>
       <c r="C2" t="n">
         <v>29.74375299702789</v>
@@ -2730,7 +2730,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03204649995313957</v>
+        <v>0.0324668749817647</v>
       </c>
       <c r="C2" t="n">
         <v>24.91154322693891</v>
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03308841702528298</v>
+        <v>0.0321703749941662</v>
       </c>
       <c r="C2" t="n">
         <v>27.48236608914779</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04262779100099578</v>
+        <v>0.04235599999083206</v>
       </c>
       <c r="C2" t="n">
         <v>33.08915691384912</v>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02742812497308478</v>
+        <v>0.02718012500554323</v>
       </c>
       <c r="C2" t="n">
         <v>18.05881459920804</v>
@@ -2994,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02932620898354799</v>
+        <v>0.02947433298686519</v>
       </c>
       <c r="C2" t="n">
         <v>25.7887567622325</v>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03101245901780203</v>
+        <v>0.03143754199845716</v>
       </c>
       <c r="C2" t="n">
         <v>30.68494652831196</v>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02908012497937307</v>
+        <v>0.02826333302073181</v>
       </c>
       <c r="C2" t="n">
         <v>28.15303935249008</v>
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03739854198647663</v>
+        <v>0.03729029098758474</v>
       </c>
       <c r="C2" t="n">
         <v>24.13078238771159</v>
@@ -3258,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0341021660133265</v>
+        <v>0.03373212501173839</v>
       </c>
       <c r="C2" t="n">
         <v>23.10637677915529</v>
@@ -3324,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04193341598147526</v>
+        <v>0.04168049996951595</v>
       </c>
       <c r="C2" t="n">
         <v>32.13854482346693</v>
@@ -3390,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0298945420072414</v>
+        <v>0.02936362498439848</v>
       </c>
       <c r="C2" t="n">
         <v>27.1688126855761</v>
@@ -3456,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02481929102214053</v>
+        <v>0.02430320798885077</v>
       </c>
       <c r="C2" t="n">
         <v>27.79007522835755</v>
@@ -3522,7 +3522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02532275003613904</v>
+        <v>0.02523804199881852</v>
       </c>
       <c r="C2" t="n">
         <v>24.58158924675276</v>
@@ -3588,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03222229098901153</v>
+        <v>0.03154079196974635</v>
       </c>
       <c r="C2" t="n">
         <v>28.07335806613609</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03162679204251617</v>
+        <v>0.03162745904410258</v>
       </c>
       <c r="C2" t="n">
         <v>28.29560009078929</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02896945900283754</v>
+        <v>0.02888641704339534</v>
       </c>
       <c r="C2" t="n">
         <v>26.16044320383183</v>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03610800002934411</v>
+        <v>0.03612983296625316</v>
       </c>
       <c r="C2" t="n">
         <v>30.67072474801884</v>
@@ -3852,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03068650001659989</v>
+        <v>0.03055812499951571</v>
       </c>
       <c r="C2" t="n">
         <v>22.24620403017808</v>
@@ -3918,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04071804200066254</v>
+        <v>0.04085420799674466</v>
       </c>
       <c r="C2" t="n">
         <v>23.44320602715669</v>
@@ -3984,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03750550001859665</v>
+        <v>0.03728191694244742</v>
       </c>
       <c r="C2" t="n">
         <v>26.41894103186296</v>
@@ -4050,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03292470797896385</v>
+        <v>0.0325272079790011</v>
       </c>
       <c r="C2" t="n">
         <v>31.69069203021384</v>
@@ -4116,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02704187500057742</v>
+        <v>0.02678216702770442</v>
       </c>
       <c r="C2" t="n">
         <v>26.59622656827356</v>
@@ -4182,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03104587498819456</v>
+        <v>0.03092033299617469</v>
       </c>
       <c r="C2" t="n">
         <v>25.84431517983234</v>
@@ -4248,7 +4248,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03441024996573105</v>
+        <v>0.03338349994737655</v>
       </c>
       <c r="C2" t="n">
         <v>23.066359406831</v>
@@ -4314,7 +4314,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03069437498925254</v>
+        <v>0.03054708294803277</v>
       </c>
       <c r="C2" t="n">
         <v>26.383680238381</v>
@@ -4380,7 +4380,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0382320000207983</v>
+        <v>0.03754504199605435</v>
       </c>
       <c r="C2" t="n">
         <v>24.11510503866736</v>
@@ -4446,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03653316700365394</v>
+        <v>0.03642629098612815</v>
       </c>
       <c r="C2" t="n">
         <v>31.15274486568289</v>
@@ -4512,7 +4512,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02548075001686811</v>
+        <v>0.02529908297583461</v>
       </c>
       <c r="C2" t="n">
         <v>25.10515123146655</v>
@@ -4578,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02337462495779619</v>
+        <v>0.02316354104550555</v>
       </c>
       <c r="C2" t="n">
         <v>21.40247859344191</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03453416598495096</v>
+        <v>0.03485216700937599</v>
       </c>
       <c r="C2" t="n">
         <v>28.84499232601139</v>
@@ -4710,7 +4710,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0349068749928847</v>
+        <v>0.03453349997289479</v>
       </c>
       <c r="C2" t="n">
         <v>31.96300888133719</v>
@@ -4776,7 +4776,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03741333301877603</v>
+        <v>0.03719166596420109</v>
       </c>
       <c r="C2" t="n">
         <v>19.1874685605234</v>
@@ -4842,7 +4842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03500145900761709</v>
+        <v>0.03466754104010761</v>
       </c>
       <c r="C2" t="n">
         <v>22.97599057801336</v>
@@ -4908,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03431216697208583</v>
+        <v>0.03394649998517707</v>
       </c>
       <c r="C2" t="n">
         <v>29.8014388645108</v>
@@ -4974,7 +4974,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03529895801329985</v>
+        <v>0.03379050001967698</v>
       </c>
       <c r="C2" t="n">
         <v>24.58878539776038</v>
@@ -5040,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02848445903509855</v>
+        <v>0.0281287080142647</v>
       </c>
       <c r="C2" t="n">
         <v>26.48750095162407</v>
@@ -5106,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0289857080206275</v>
+        <v>0.02885654201963916</v>
       </c>
       <c r="C2" t="n">
         <v>20.87484769185441</v>
@@ -5172,7 +5172,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02876058302354068</v>
+        <v>0.02871058299206197</v>
       </c>
       <c r="C2" t="n">
         <v>30.3521143176178</v>
@@ -5238,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02944966702489182</v>
+        <v>0.02918787498492748</v>
       </c>
       <c r="C2" t="n">
         <v>19.03386101859335</v>
@@ -5304,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03524141601519659</v>
+        <v>0.03536445798818022</v>
       </c>
       <c r="C2" t="n">
         <v>23.19640566381431</v>
@@ -5370,7 +5370,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03059320797910914</v>
+        <v>0.03016033297171816</v>
       </c>
       <c r="C2" t="n">
         <v>20.16017652381561</v>
@@ -5436,7 +5436,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04003083298448473</v>
+        <v>0.03985999996075407</v>
       </c>
       <c r="C2" t="n">
         <v>22.13780947150403</v>
@@ -5502,7 +5502,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03131674998439848</v>
+        <v>0.03108599997358397</v>
       </c>
       <c r="C2" t="n">
         <v>29.29725439327199</v>
@@ -5568,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03511408303165808</v>
+        <v>0.0350414999993518</v>
       </c>
       <c r="C2" t="n">
         <v>24.01116811918489</v>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03627791604958475</v>
+        <v>0.03621670900611207</v>
       </c>
       <c r="C2" t="n">
         <v>25.0046187156633</v>
@@ -5700,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02909954101778567</v>
+        <v>0.02827045798767358</v>
       </c>
       <c r="C2" t="n">
         <v>32.93361061351427</v>
@@ -5766,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03028829203685746</v>
+        <v>0.03039387497119606</v>
       </c>
       <c r="C2" t="n">
         <v>26.95558676956336</v>
@@ -5832,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03057033300865442</v>
+        <v>0.0300556659931317</v>
       </c>
       <c r="C2" t="n">
         <v>29.22535108295815</v>
@@ -5898,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02522525005042553</v>
+        <v>0.02552295796340331</v>
       </c>
       <c r="C2" t="n">
         <v>22.95345139908935</v>
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.036670041969046</v>
+        <v>0.03629208402708173</v>
       </c>
       <c r="C2" t="n">
         <v>28.28166847430387</v>
@@ -6030,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03048162499908358</v>
+        <v>0.03013304196065292</v>
       </c>
       <c r="C2" t="n">
         <v>25.74364289621601</v>
@@ -6096,7 +6096,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0293622090248391</v>
+        <v>0.02948658401146531</v>
       </c>
       <c r="C2" t="n">
         <v>27.36872350918075</v>
@@ -6162,7 +6162,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02920016698772088</v>
+        <v>0.02872170804766938</v>
       </c>
       <c r="C2" t="n">
         <v>27.39725373853555</v>
@@ -6228,7 +6228,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03027116699377075</v>
+        <v>0.03015274996869266</v>
       </c>
       <c r="C2" t="n">
         <v>22.09668709982884</v>
@@ -6294,7 +6294,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02976420801132917</v>
+        <v>0.02947929204674438</v>
       </c>
       <c r="C2" t="n">
         <v>23.74450288537857</v>
@@ -6360,7 +6360,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02971791697200388</v>
+        <v>0.02970812498824671</v>
       </c>
       <c r="C2" t="n">
         <v>24.5022837145464</v>
@@ -6426,7 +6426,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03522291599074379</v>
+        <v>0.03381320799235255</v>
       </c>
       <c r="C2" t="n">
         <v>25.76556072725754</v>
@@ -6492,7 +6492,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03172937501221895</v>
+        <v>0.03177554201101884</v>
       </c>
       <c r="C2" t="n">
         <v>27.65887615876256</v>
@@ -6558,7 +6558,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03434216597815976</v>
+        <v>0.03388504200847819</v>
       </c>
       <c r="C2" t="n">
         <v>21.94297867107104</v>
@@ -6624,7 +6624,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03092774999095127</v>
+        <v>0.03079741704277694</v>
       </c>
       <c r="C2" t="n">
         <v>29.64842419577577</v>
@@ -6690,7 +6690,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02852487500058487</v>
+        <v>0.02797183400252834</v>
       </c>
       <c r="C2" t="n">
         <v>24.25086141006013</v>
@@ -6756,7 +6756,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03072254196740687</v>
+        <v>0.03037487500114366</v>
       </c>
       <c r="C2" t="n">
         <v>21.34958531531084</v>
@@ -6822,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02890720800496638</v>
+        <v>0.02886816702084616</v>
       </c>
       <c r="C2" t="n">
         <v>23.4016800916731</v>
@@ -6888,7 +6888,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04456420801579952</v>
+        <v>0.04441916599171236</v>
       </c>
       <c r="C2" t="n">
         <v>28.08427886819091</v>
@@ -6954,7 +6954,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03679566696519032</v>
+        <v>0.03731262497603893</v>
       </c>
       <c r="C2" t="n">
         <v>24.01826489266311</v>
@@ -7020,7 +7020,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04320487502263859</v>
+        <v>0.04324333398835734</v>
       </c>
       <c r="C2" t="n">
         <v>30.51309485044004</v>
@@ -7086,7 +7086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0365390419610776</v>
+        <v>0.03592408302938566</v>
       </c>
       <c r="C2" t="n">
         <v>30.63311186116157</v>
